--- a/Table/Enum/Enum.xlsx
+++ b/Table/Enum/Enum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581AE276-0EE4-42B0-AAD8-2BB5C97E4284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A337518D-1974-4ADD-A113-7598B561E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
   <si>
     <t>!Enum</t>
   </si>
@@ -173,6 +173,46 @@
   </si>
   <si>
     <t>NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 단일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌덤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleConstType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPMidBonus</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HP 보너스 중간 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP 보너스 최대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPMaxBonus</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -522,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -787,7 +827,7 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
@@ -799,7 +839,7 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
@@ -811,7 +851,7 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
@@ -823,7 +863,7 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
@@ -837,26 +877,50 @@
         <v>16</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="3"/>
     </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="3"/>
+    </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="3"/>
+      <c r="B33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
@@ -864,11 +928,11 @@
       <c r="D34" s="2"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="3"/>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="2"/>
@@ -882,11 +946,11 @@
       <c r="D38" s="2"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="3"/>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
@@ -900,6 +964,12 @@
       <c r="D42" s="2"/>
       <c r="E42" s="3"/>
     </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="3"/>
+    </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -912,12 +982,6 @@
       <c r="D45" s="2"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="3"/>
-    </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -930,18 +994,18 @@
       <c r="D48" s="2"/>
       <c r="E48" s="3"/>
     </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3"/>
+    </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="3"/>
-    </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -954,23 +1018,11 @@
       <c r="D53" s="2"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="3"/>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Table/Enum/Enum.xlsx
+++ b/Table/Enum/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A337518D-1974-4ADD-A113-7598B561E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC91ABE-12A4-4976-938F-A0E8461DDF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>!Enum</t>
   </si>
@@ -213,6 +213,86 @@
   </si>
   <si>
     <t>HPMaxBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stun</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도트 데미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffExecuteType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnEnd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>턴 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>턴 종료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -929,34 +1009,88 @@
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="3"/>
     </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="D37" s="2"/>
-      <c r="E37" s="3"/>
+      <c r="E37" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="3"/>
+      <c r="E38" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="3"/>
+      <c r="E39" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="3"/>
+      <c r="B41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="2"/>
@@ -965,64 +1099,52 @@
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="3"/>
+      <c r="E44" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="D45" s="2"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="3"/>
+      <c r="E45" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Table/Enum/Enum.xlsx
+++ b/Table/Enum/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC91ABE-12A4-4976-938F-A0E8461DDF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F25E9-1282-42C0-8361-1C85374529F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
   <si>
     <t>!Enum</t>
   </si>
@@ -220,22 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AddATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Stun</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -244,22 +228,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스턴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,6 +261,70 @@
   </si>
   <si>
     <t>턴 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowPATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowPDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowEATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddEATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddEDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowEDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -1023,11 +1055,11 @@
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
@@ -1035,11 +1067,11 @@
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
@@ -1047,11 +1079,11 @@
         <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
@@ -1059,11 +1091,11 @@
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
@@ -1071,11 +1103,11 @@
         <v>1</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
@@ -1083,41 +1115,47 @@
         <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="3"/>
+      <c r="E42" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D43" s="2"/>
-      <c r="E43" s="3"/>
+      <c r="E43" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
@@ -1125,29 +1163,72 @@
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E45" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>67</v>
+      <c r="E50" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Table/Enum/Enum.xlsx
+++ b/Table/Enum/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F25E9-1282-42C0-8361-1C85374529F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E3C241-52B5-41FC-9A78-EB5C67420E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>!Enum</t>
   </si>
@@ -224,107 +224,110 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>스턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도트 데미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffExecuteType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnEnd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>턴 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>턴 종료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowPATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowPDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowEATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddEATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddEDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LowEDEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Dot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도트 데미지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffExecuteType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TurnStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TurnEnd</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>턴 시작</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>턴 종료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddPATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddPDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowPATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowPDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowEATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddEATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddEDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LowEDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 감소</t>
+  </si>
+  <si>
+    <t>Max</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -674,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -1055,11 +1058,11 @@
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
@@ -1067,11 +1070,11 @@
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
@@ -1079,11 +1082,11 @@
         <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
@@ -1091,11 +1094,11 @@
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
@@ -1103,11 +1106,11 @@
         <v>1</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
@@ -1115,11 +1118,11 @@
         <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -1127,11 +1130,11 @@
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
@@ -1139,11 +1142,11 @@
         <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
@@ -1155,7 +1158,7 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
@@ -1163,53 +1166,53 @@
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
@@ -1217,13 +1220,25 @@
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>59</v>
+      <c r="E51" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Table/Enum/Enum.xlsx
+++ b/Table/Enum/Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E3C241-52B5-41FC-9A78-EB5C67420E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA885AE-9B2E-4AEE-84B5-84807C301A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26430" yWindow="1680" windowWidth="23745" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
   <si>
     <t>!Enum</t>
   </si>
@@ -328,6 +328,34 @@
   </si>
   <si>
     <t>Max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillValueType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디버프</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -677,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -928,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3"/>
@@ -938,11 +966,11 @@
         <v>1</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
@@ -950,11 +978,11 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
@@ -962,65 +990,65 @@
         <v>1</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E27" s="3" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
@@ -1028,53 +1056,53 @@
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="E34" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
@@ -1082,47 +1110,41 @@
         <v>1</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E38" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
@@ -1130,11 +1152,11 @@
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
@@ -1142,11 +1164,11 @@
         <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
@@ -1154,11 +1176,11 @@
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
@@ -1166,11 +1188,11 @@
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
@@ -1178,41 +1200,47 @@
         <v>1</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D46" s="2"/>
       <c r="E46" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="D47" s="2"/>
-      <c r="E47" s="3"/>
+      <c r="E47" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="3"/>
+      <c r="E48" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
@@ -1220,11 +1248,11 @@
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
@@ -1232,12 +1260,66 @@
         <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>58</v>
       </c>
     </row>
